--- a/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_edge_bh.xlsx
+++ b/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_edge_bh.xlsx
@@ -1133,7 +1133,7 @@
         <v>2.667044553297952e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1193,7 +1193,7 @@
         <v>2.669910354539522e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>2.675649247721808e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         <v>0.0006451158437926242</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001658869312609605</v>
+        <v>0.001055644108024294</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1501,7 +1501,7 @@
         <v>2.667044553297952e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1561,7 +1561,7 @@
         <v>2.669910354539522e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>2.571042765083602e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>7.135064660591489e-05</v>
+        <v>4.480156879906284e-05</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -1681,7 +1681,7 @@
         <v>0.001886167459244937</v>
       </c>
       <c r="K20" t="n">
-        <v>0.004526801902187849</v>
+        <v>0.00295226211012251</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -2061,7 +2061,7 @@
         <v>0.001886167459244937</v>
       </c>
       <c r="K26" t="n">
-        <v>0.004526801902187849</v>
+        <v>0.00295226211012251</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -2249,7 +2249,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="K29" t="n">
-        <v>5.416435932528189e-13</v>
+        <v>3.074193367110594e-13</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -2309,7 +2309,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="K30" t="n">
-        <v>5.416435932528189e-13</v>
+        <v>3.074193367110594e-13</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
@@ -2617,7 +2617,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="K35" t="n">
-        <v>5.416435932528189e-13</v>
+        <v>3.074193367110594e-13</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -2677,7 +2677,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="K36" t="n">
-        <v>5.416435932528189e-13</v>
+        <v>3.074193367110594e-13</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         <v>1.579793813654055e-13</v>
       </c>
       <c r="K37" t="n">
-        <v>5.416435932528189e-13</v>
+        <v>3.074193367110594e-13</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -3337,41 +3337,37 @@
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3401,41 +3397,37 @@
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3465,41 +3457,37 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3718,44 +3706,40 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-12.12</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3782,44 +3766,40 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="G54" t="n">
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-12.12</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3846,44 +3826,40 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>87.88</v>
       </c>
       <c r="G55" t="n">
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-12.12</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>2.337119062755719e-67</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3925,7 +3901,7 @@
         <v>2.387238385100547e-67</v>
       </c>
       <c r="K56" t="n">
-        <v>1.718811637272394e-66</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -3973,41 +3949,37 @@
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>6.78</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>93.22</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4037,41 +4009,37 @@
         <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>91.28</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4101,41 +4069,37 @@
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>14.31</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4165,41 +4129,37 @@
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>14.31</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4229,41 +4189,37 @@
         <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>14.31</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4293,10 +4249,10 @@
         <v>3.57</v>
       </c>
       <c r="G62" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H62" t="n">
-        <v>-96.43000000000001</v>
+        <v>-81.47999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -4305,7 +4261,7 @@
         <v>2.387238385100547e-67</v>
       </c>
       <c r="K62" t="n">
-        <v>1.718811637272394e-66</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -4350,44 +4306,40 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>6.78</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-78.88</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4414,44 +4366,40 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>85.69</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-77.39999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>5.37128636647623e-67</v>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4481,25 +4429,25 @@
         <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>40.28</v>
+        <v>36.76</v>
       </c>
       <c r="H65" t="n">
-        <v>59.72</v>
+        <v>63.24</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K65" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4541,25 +4489,25 @@
         <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>41.67</v>
+        <v>38.24</v>
       </c>
       <c r="H66" t="n">
-        <v>58.33</v>
+        <v>61.76</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K66" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -4601,25 +4549,25 @@
         <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>43.06</v>
+        <v>39.71</v>
       </c>
       <c r="H67" t="n">
-        <v>56.94</v>
+        <v>60.29</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K67" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -4661,41 +4609,37 @@
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>4.409999999999997</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2.357850315905791e-71</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>1.5433202067747e-70</v>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4725,41 +4669,37 @@
         <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>4.409999999999997</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2.357850315905791e-71</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>1.5433202067747e-70</v>
       </c>
       <c r="L69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4789,41 +4729,37 @@
         <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>4.409999999999997</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>2.357850315905791e-71</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>1.5433202067747e-70</v>
       </c>
       <c r="L70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4850,28 +4786,28 @@
         <v>416</v>
       </c>
       <c r="F71" t="n">
-        <v>40.28</v>
+        <v>36.76</v>
       </c>
       <c r="G71" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H71" t="n">
-        <v>-59.72</v>
+        <v>-58.83000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K71" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4910,28 +4846,28 @@
         <v>416</v>
       </c>
       <c r="F72" t="n">
-        <v>41.67</v>
+        <v>38.24</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H72" t="n">
-        <v>-58.33</v>
+        <v>-57.35</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K72" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4970,28 +4906,28 @@
         <v>416</v>
       </c>
       <c r="F73" t="n">
-        <v>43.06</v>
+        <v>39.71</v>
       </c>
       <c r="G73" t="n">
-        <v>100</v>
+        <v>95.59</v>
       </c>
       <c r="H73" t="n">
-        <v>-56.94</v>
+        <v>-55.88</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1.158550930584792e-58</v>
+        <v>1.078866486479425e-70</v>
       </c>
       <c r="K73" t="n">
-        <v>5.213479187631564e-58</v>
+        <v>4.569316883912859e-70</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -5159,7 +5095,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0006277901785714286</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -5207,25 +5143,25 @@
         <v>58.115</v>
       </c>
       <c r="G3" t="n">
-        <v>38.395</v>
+        <v>36.05</v>
       </c>
       <c r="H3" t="n">
-        <v>20.2</v>
+        <v>17.235</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01513671875</v>
+        <v>0.00341796875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01879040948275862</v>
+        <v>0.004242995689655173</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8194444444444444</v>
+        <v>0.8680555555555556</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5273,19 +5209,19 @@
         <v>10.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0.03125</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0375</v>
+        <v>0.03688524590163934</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5339,7 +5275,7 @@
         <v>0.125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -5399,7 +5335,7 @@
         <v>0.125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -5459,7 +5395,7 @@
         <v>0.125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -5510,7 +5446,7 @@
         <v>64.29000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.11500000000001</v>
+        <v>-34.30500000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -5519,7 +5455,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006510416666666666</v>
+        <v>0.0006277901785714286</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -5564,28 +5500,28 @@
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>38.395</v>
+        <v>36.05</v>
       </c>
       <c r="G9" t="n">
         <v>64.29000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-27.47</v>
+        <v>-27.675</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00244140625</v>
+        <v>0.00146484375</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003138950892857143</v>
+        <v>0.001850328947368421</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.08680555555555555</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -5630,26 +5566,26 @@
         <v>64.29000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-19.485</v>
+        <v>-12.34</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.015625</v>
+        <v>0.03125</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01906779661016949</v>
+        <v>0.03688524590163934</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5684,22 +5620,22 @@
         <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>54.55</v>
+        <v>54.35</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>-45.45</v>
+        <v>-45.65</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.384185791015625e-07</v>
+        <v>2.698702240967945e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.598269654623926e-05</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -5747,10 +5683,10 @@
         <v>21.13</v>
       </c>
       <c r="G12" t="n">
-        <v>60.34</v>
+        <v>62.07</v>
       </c>
       <c r="H12" t="n">
-        <v>-38.92</v>
+        <v>-40.61</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -5759,7 +5695,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -5819,7 +5755,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -5864,7 +5800,7 @@
         <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>54.55</v>
+        <v>54.35</v>
       </c>
       <c r="G14" t="n">
         <v>25.175</v>
@@ -5879,7 +5815,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -5939,7 +5875,7 @@
         <v>0.006032705307006836</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00762025933516653</v>
+        <v>0.007361945459398173</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -5999,7 +5935,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -6059,7 +5995,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -6104,13 +6040,13 @@
         <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>60.34</v>
+        <v>62.07</v>
       </c>
       <c r="G18" t="n">
         <v>25.175</v>
       </c>
       <c r="H18" t="n">
-        <v>34.27</v>
+        <v>39.11500000000001</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -6119,7 +6055,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>3.365909352022059e-07</v>
+        <v>3.4332275390625e-07</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -6170,7 +6106,7 @@
         <v>25.175</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6500000000000021</v>
+        <v>1.274999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>116</v>
@@ -6179,13 +6115,13 @@
         <v>0.5202305316925049</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5590537056994083</v>
+        <v>0.5350942611694336</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5311909262759924</v>
+        <v>0.5293005671077504</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -6224,28 +6160,28 @@
         <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>48.96</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7949999999999982</v>
+        <v>-0.375</v>
       </c>
       <c r="I20" t="n">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7880452788189998</v>
+        <v>0.5729419086138248</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8105608582138284</v>
+        <v>0.5810115129604984</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4829931972789115</v>
+        <v>0.465702947845805</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -6290,22 +6226,22 @@
         <v>14.09</v>
       </c>
       <c r="H21" t="n">
-        <v>3.045000000000001</v>
+        <v>3.215</v>
       </c>
       <c r="I21" t="n">
         <v>327</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1195330456099672</v>
+        <v>0.1195222060708891</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6179138321995464</v>
+        <v>0.61281179138322</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -6350,22 +6286,22 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>1.155</v>
       </c>
       <c r="I22" t="n">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5359416592734699</v>
+        <v>0.302267743253409</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5674676392307328</v>
+        <v>0.3154098190470355</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5918367346938775</v>
+        <v>0.5912698412698413</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -6404,13 +6340,13 @@
         <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>48.96</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
         <v>19.55</v>
       </c>
       <c r="H23" t="n">
-        <v>28.1625</v>
+        <v>28.1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -6419,7 +6355,7 @@
         <v>4.547473508864641e-13</v>
       </c>
       <c r="K23" t="n">
-        <v>8.185452315956354e-13</v>
+        <v>7.985807137518394e-13</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -6479,13 +6415,13 @@
         <v>0.9451720434011086</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9584843257025326</v>
+        <v>0.9451720434011085</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5090702947845805</v>
+        <v>0.5085034013605442</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -6539,7 +6475,7 @@
         <v>4.001776687800884e-11</v>
       </c>
       <c r="K25" t="n">
-        <v>6.700649337713109e-11</v>
+        <v>6.860188607658659e-11</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -6599,7 +6535,7 @@
         <v>4.547473508864641e-13</v>
       </c>
       <c r="K26" t="n">
-        <v>8.185452315956354e-13</v>
+        <v>7.985807137518394e-13</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -6650,22 +6586,22 @@
         <v>19.55</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5624999999999982</v>
+        <v>-0.4375</v>
       </c>
       <c r="I27" t="n">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1108839245157054</v>
+        <v>0.1668257985193122</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1287684284698514</v>
+        <v>0.1766390807851541</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4421768707482993</v>
+        <v>0.4467120181405896</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -6710,22 +6646,22 @@
         <v>19.55</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.3525</v>
+        <v>-4.984999999999998</v>
       </c>
       <c r="I28" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J28" t="n">
-        <v>1.271944256586721e-06</v>
+        <v>1.789447196642868e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>1.761153586043152e-06</v>
+        <v>2.477696118428586e-06</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2670068027210885</v>
+        <v>0.2794784580498866</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -6767,25 +6703,25 @@
         <v>47.14</v>
       </c>
       <c r="G29" t="n">
-        <v>35.56</v>
+        <v>35.33</v>
       </c>
       <c r="H29" t="n">
-        <v>13.16</v>
+        <v>13.27</v>
       </c>
       <c r="I29" t="n">
-        <v>20325.5</v>
+        <v>19144.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.076116259135886e-38</v>
+        <v>8.198269450115605e-41</v>
       </c>
       <c r="K29" t="n">
-        <v>2.582679021926126e-38</v>
+        <v>1.844610626276011e-40</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8567785197012951</v>
+        <v>0.8631554329768875</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -6827,25 +6763,25 @@
         <v>44.505</v>
       </c>
       <c r="G30" t="n">
-        <v>38.46</v>
+        <v>38.615</v>
       </c>
       <c r="H30" t="n">
-        <v>8.015000000000001</v>
+        <v>7.989999999999995</v>
       </c>
       <c r="I30" t="n">
-        <v>32235.5</v>
+        <v>33414</v>
       </c>
       <c r="J30" t="n">
-        <v>1.36613881292803e-20</v>
+        <v>4.029804851057404e-19</v>
       </c>
       <c r="K30" t="n">
-        <v>2.892999839141711e-20</v>
+        <v>7.635419717792976e-19</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6872308511153046</v>
+        <v>0.6800212899791939</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -6887,25 +6823,25 @@
         <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>41.41500000000001</v>
+        <v>41.325</v>
       </c>
       <c r="H31" t="n">
-        <v>8.829999999999998</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>20423.5</v>
+        <v>20483</v>
       </c>
       <c r="J31" t="n">
-        <v>1.982311888688427e-37</v>
+        <v>2.524275885979632e-37</v>
       </c>
       <c r="K31" t="n">
-        <v>4.460201749548961e-37</v>
+        <v>5.507511023955561e-37</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7265689263076403</v>
+        <v>0.725740310640151</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -6953,19 +6889,19 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>45571.5</v>
+        <v>45835.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0.06126647480147846</v>
+        <v>0.07574544647555578</v>
       </c>
       <c r="K32" t="n">
-        <v>0.07231452763453196</v>
+        <v>0.08656622454349233</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4751959645812164</v>
+        <v>0.4765850550797568</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -7019,7 +6955,7 @@
         <v>2.543467683332074e-45</v>
       </c>
       <c r="K33" t="n">
-        <v>6.78258048888553e-45</v>
+        <v>5.9074088129003e-45</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
@@ -7079,7 +7015,7 @@
         <v>1.632610969639346e-10</v>
       </c>
       <c r="K34" t="n">
-        <v>2.671545223046202e-10</v>
+        <v>2.733674181721696e-10</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -7124,28 +7060,28 @@
         <v>498</v>
       </c>
       <c r="F35" t="n">
-        <v>35.56</v>
+        <v>35.33</v>
       </c>
       <c r="G35" t="n">
         <v>46.79000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-11.845</v>
+        <v>-11.945</v>
       </c>
       <c r="I35" t="n">
-        <v>15242</v>
+        <v>14443.5</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15978172770192e-48</v>
+        <v>1.309787992495416e-49</v>
       </c>
       <c r="K35" t="n">
-        <v>9.100171375781529e-48</v>
+        <v>3.251887429643791e-49</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1399654844276705</v>
+        <v>0.1349272592377542</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -7184,28 +7120,28 @@
         <v>498</v>
       </c>
       <c r="F36" t="n">
-        <v>38.46</v>
+        <v>38.615</v>
       </c>
       <c r="G36" t="n">
         <v>46.79000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>-11.615</v>
+        <v>-11.62</v>
       </c>
       <c r="I36" t="n">
-        <v>13326</v>
+        <v>14207.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4.22767059977073e-52</v>
+        <v>2.674980611607204e-50</v>
       </c>
       <c r="K36" t="n">
-        <v>1.268301179931219e-51</v>
+        <v>6.878521572704238e-50</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.199490734020419</v>
+        <v>0.2067184400251609</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -7244,28 +7180,28 @@
         <v>498</v>
       </c>
       <c r="F37" t="n">
-        <v>41.41500000000001</v>
+        <v>41.325</v>
       </c>
       <c r="G37" t="n">
         <v>46.79000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.912500000000001</v>
+        <v>-5.700000000000003</v>
       </c>
       <c r="I37" t="n">
-        <v>9459</v>
+        <v>9424</v>
       </c>
       <c r="J37" t="n">
-        <v>8.280354060471045e-47</v>
+        <v>6.815360907739107e-47</v>
       </c>
       <c r="K37" t="n">
-        <v>2.293021124438136e-46</v>
+        <v>1.635686617857386e-46</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2981766423122208</v>
+        <v>0.2974528636634893</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -7307,13 +7243,13 @@
         <v>39.34</v>
       </c>
       <c r="G38" t="n">
-        <v>60.065</v>
+        <v>60.5</v>
       </c>
       <c r="H38" t="n">
-        <v>-19.795</v>
+        <v>-19.79500000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>71241</v>
+        <v>72101.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7325,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1258744668091515</v>
+        <v>0.126738013351189</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -7364,16 +7300,16 @@
         <v>2664</v>
       </c>
       <c r="F39" t="n">
-        <v>22.78</v>
+        <v>22.73</v>
       </c>
       <c r="G39" t="n">
-        <v>31.39</v>
+        <v>31.45</v>
       </c>
       <c r="H39" t="n">
-        <v>-8.145000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="I39" t="n">
-        <v>36365</v>
+        <v>35185.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7385,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0571383602070539</v>
+        <v>0.05802262002993985</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -7424,16 +7360,16 @@
         <v>2664</v>
       </c>
       <c r="F40" t="n">
-        <v>14.04</v>
+        <v>14.05</v>
       </c>
       <c r="G40" t="n">
-        <v>22.19</v>
+        <v>22.3</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.510000000000002</v>
+        <v>-7.550000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>74665</v>
+        <v>73260</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7445,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.07098807704100497</v>
+        <v>0.07098913384104825</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -7490,10 +7426,10 @@
         <v>22.1</v>
       </c>
       <c r="H41" t="n">
-        <v>17.2325</v>
+        <v>17.245</v>
       </c>
       <c r="I41" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7505,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9991217991640289</v>
+        <v>0.999122785510736</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -7544,28 +7480,28 @@
         <v>2664</v>
       </c>
       <c r="F42" t="n">
-        <v>22.78</v>
+        <v>22.73</v>
       </c>
       <c r="G42" t="n">
         <v>22.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7749999999999986</v>
+        <v>0.7675000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>1263538</v>
+        <v>1299783</v>
       </c>
       <c r="J42" t="n">
-        <v>1.165092323111101e-37</v>
+        <v>1.017683742662625e-32</v>
       </c>
       <c r="K42" t="n">
-        <v>2.706020879483847e-37</v>
+        <v>2.093520842048828e-32</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5823916540414288</v>
+        <v>0.5745842266816366</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -7604,16 +7540,16 @@
         <v>2664</v>
       </c>
       <c r="F43" t="n">
-        <v>14.04</v>
+        <v>14.05</v>
       </c>
       <c r="G43" t="n">
         <v>22.1</v>
       </c>
       <c r="H43" t="n">
-        <v>-7.435000000000001</v>
+        <v>-7.432499999999998</v>
       </c>
       <c r="I43" t="n">
-        <v>80992</v>
+        <v>80698</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -7625,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0.07150689540892244</v>
+        <v>0.07182041275509744</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -7664,16 +7600,16 @@
         <v>2664</v>
       </c>
       <c r="F44" t="n">
-        <v>60.065</v>
+        <v>60.5</v>
       </c>
       <c r="G44" t="n">
         <v>22.1</v>
       </c>
       <c r="H44" t="n">
-        <v>37.425</v>
+        <v>37.86999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -7685,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.999397060348637</v>
+        <v>0.9993807856279703</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -7724,16 +7660,16 @@
         <v>2664</v>
       </c>
       <c r="F45" t="n">
-        <v>31.39</v>
+        <v>31.45</v>
       </c>
       <c r="G45" t="n">
         <v>22.1</v>
       </c>
       <c r="H45" t="n">
-        <v>8.692500000000001</v>
+        <v>8.699999999999998</v>
       </c>
       <c r="I45" t="n">
-        <v>45515.5</v>
+        <v>47062</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -7745,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9499137369351334</v>
+        <v>0.9491083143954766</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -7784,28 +7720,28 @@
         <v>2664</v>
       </c>
       <c r="F46" t="n">
-        <v>22.19</v>
+        <v>22.3</v>
       </c>
       <c r="G46" t="n">
         <v>22.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.07999999999999829</v>
       </c>
       <c r="I46" t="n">
-        <v>1752253</v>
+        <v>1690004</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6381173790641197</v>
+        <v>0.04126911508948807</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6658616129364727</v>
+        <v>0.04792542397488937</v>
       </c>
       <c r="L46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0.50688322049527</v>
+        <v>0.5148245796472147</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -7844,37 +7780,37 @@
         <v>400</v>
       </c>
       <c r="F47" t="n">
-        <v>11.39</v>
+        <v>11.95</v>
       </c>
       <c r="G47" t="n">
-        <v>6.77</v>
+        <v>12.3</v>
       </c>
       <c r="H47" t="n">
-        <v>4.770000000000001</v>
+        <v>-0.7949999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>18720</v>
+        <v>28116</v>
       </c>
       <c r="J47" t="n">
-        <v>3.979916755555636e-20</v>
+        <v>3.181032888973262e-07</v>
       </c>
       <c r="K47" t="n">
-        <v>8.187257325714451e-20</v>
+        <v>4.490869960903429e-07</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.707984375</v>
+        <v>0.4575875</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>ApproachB</t>
+          <t>ApproachA</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -7904,28 +7840,28 @@
         <v>400</v>
       </c>
       <c r="F48" t="n">
-        <v>8.49</v>
+        <v>8.74</v>
       </c>
       <c r="G48" t="n">
-        <v>5.68</v>
+        <v>9.649999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>2.68</v>
+        <v>-1.755</v>
       </c>
       <c r="I48" t="n">
-        <v>23748</v>
+        <v>26537</v>
       </c>
       <c r="J48" t="n">
-        <v>1.577466534777955e-12</v>
+        <v>4.568827717015505e-09</v>
       </c>
       <c r="K48" t="n">
-        <v>2.770185134244213e-12</v>
+        <v>7.476263536934463e-09</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0.636746875</v>
+        <v>0.409003125</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -7934,7 +7870,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>ApproachB</t>
+          <t>ApproachA</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -7964,37 +7900,37 @@
         <v>400</v>
       </c>
       <c r="F49" t="n">
-        <v>8.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>4.885</v>
+        <v>7.925000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>2.68</v>
+        <v>-1.125</v>
       </c>
       <c r="I49" t="n">
-        <v>19061.5</v>
+        <v>29939</v>
       </c>
       <c r="J49" t="n">
-        <v>9.62790028652568e-20</v>
+        <v>1.549810411329673e-05</v>
       </c>
       <c r="K49" t="n">
-        <v>1.925580057305136e-19</v>
+        <v>2.105402822938424e-05</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.66145625</v>
+        <v>0.437790625</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>ApproachB</t>
+          <t>ApproachA</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -8024,28 +7960,28 @@
         <v>400</v>
       </c>
       <c r="F50" t="n">
-        <v>11.39</v>
+        <v>11.95</v>
       </c>
       <c r="G50" t="n">
         <v>6.45</v>
       </c>
       <c r="H50" t="n">
-        <v>5.1175</v>
+        <v>5.149999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>6896</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.306853704937671e-43</v>
+        <v>2.356748797240038e-64</v>
       </c>
       <c r="K50" t="n">
-        <v>3.360480955554011e-43</v>
+        <v>6.526381284664721e-64</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7441375</v>
+        <v>0.79935</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -8084,28 +8020,28 @@
         <v>400</v>
       </c>
       <c r="F51" t="n">
-        <v>8.49</v>
+        <v>8.74</v>
       </c>
       <c r="G51" t="n">
         <v>6.45</v>
       </c>
       <c r="H51" t="n">
-        <v>1.805</v>
+        <v>1.9825</v>
       </c>
       <c r="I51" t="n">
-        <v>12092</v>
+        <v>4068</v>
       </c>
       <c r="J51" t="n">
-        <v>1.868804585821329e-30</v>
+        <v>3.238587442323071e-51</v>
       </c>
       <c r="K51" t="n">
-        <v>4.077391823610173e-30</v>
+        <v>8.63623317952819e-51</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5722125</v>
+        <v>0.61481875</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -8144,32 +8080,32 @@
         <v>400</v>
       </c>
       <c r="F52" t="n">
-        <v>8.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G52" t="n">
         <v>6.45</v>
       </c>
       <c r="H52" t="n">
-        <v>1.765000000000001</v>
+        <v>1.805</v>
       </c>
       <c r="I52" t="n">
-        <v>17430</v>
+        <v>10361.5</v>
       </c>
       <c r="J52" t="n">
-        <v>1.768212749391498e-19</v>
+        <v>6.497900991884954e-34</v>
       </c>
       <c r="K52" t="n">
-        <v>3.44084643124832e-19</v>
+        <v>1.376026092399167e-33</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.541296875</v>
+        <v>0.581784375</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -8204,37 +8140,37 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>6.77</v>
+        <v>12.3</v>
       </c>
       <c r="G53" t="n">
         <v>6.45</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5550000000000002</v>
+        <v>6.1075</v>
       </c>
       <c r="I53" t="n">
-        <v>40059.5</v>
+        <v>14133</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9860343510059231</v>
+        <v>3.14303766068102e-29</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9860343510059231</v>
+        <v>6.28607532136204e-29</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.486375</v>
+        <v>0.7585</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -8264,37 +8200,37 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>5.68</v>
+        <v>9.649999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>6.45</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.265</v>
+        <v>3.4725</v>
       </c>
       <c r="I54" t="n">
-        <v>32255.5</v>
+        <v>18620</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0009118796520070815</v>
+        <v>2.660089628885032e-20</v>
       </c>
       <c r="K54" t="n">
-        <v>0.001193733362627452</v>
+        <v>5.176390629181684e-20</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.42413125</v>
+        <v>0.68829375</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -8324,28 +8260,28 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>4.885</v>
+        <v>7.925000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>6.45</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.84</v>
+        <v>1.98</v>
       </c>
       <c r="I55" t="n">
-        <v>24110.5</v>
+        <v>23346</v>
       </c>
       <c r="J55" t="n">
-        <v>4.822206038697908e-12</v>
+        <v>4.44936024221828e-13</v>
       </c>
       <c r="K55" t="n">
-        <v>8.266638923482129e-12</v>
+        <v>7.985807137518394e-13</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.365096875</v>
+        <v>0.6304625</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -8354,7 +8290,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -8384,22 +8320,22 @@
         <v>400</v>
       </c>
       <c r="F56" t="n">
-        <v>2.005</v>
+        <v>33.44</v>
       </c>
       <c r="G56" t="n">
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>-97.995</v>
+        <v>-66.56</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.412673020165349e-67</v>
+        <v>2.724647409244778e-67</v>
       </c>
       <c r="K56" t="n">
-        <v>1.281421616962445e-66</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -8444,32 +8380,32 @@
         <v>400</v>
       </c>
       <c r="F57" t="n">
-        <v>2.4</v>
+        <v>31.395</v>
       </c>
       <c r="G57" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.22</v>
+        <v>-68.60499999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>9591</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>9.766407979267815e-40</v>
+        <v>2.726066618836817e-67</v>
       </c>
       <c r="K57" t="n">
-        <v>2.42476336036994e-39</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -8504,32 +8440,32 @@
         <v>400</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>29.015</v>
       </c>
       <c r="G58" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7599999999999998</v>
+        <v>-70.985</v>
       </c>
       <c r="I58" t="n">
-        <v>20150</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>6.332733904399474e-18</v>
+        <v>2.727793667651373e-67</v>
       </c>
       <c r="K58" t="n">
-        <v>1.199886423991479e-17</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3795875</v>
+        <v>0</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -8564,22 +8500,22 @@
         <v>400</v>
       </c>
       <c r="F59" t="n">
-        <v>2.005</v>
+        <v>33.44</v>
       </c>
       <c r="G59" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H59" t="n">
-        <v>1.72</v>
+        <v>22.9</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.669628368671761e-67</v>
+        <v>2.729800317819466e-67</v>
       </c>
       <c r="K59" t="n">
-        <v>1.281421616962445e-66</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -8624,22 +8560,22 @@
         <v>400</v>
       </c>
       <c r="F60" t="n">
-        <v>2.4</v>
+        <v>31.395</v>
       </c>
       <c r="G60" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H60" t="n">
-        <v>2.105</v>
+        <v>20.6875</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.661073006956787e-67</v>
+        <v>2.729752294832392e-67</v>
       </c>
       <c r="K60" t="n">
-        <v>1.281421616962445e-66</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L60" t="b">
         <v>1</v>
@@ -8684,28 +8620,28 @@
         <v>400</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>29.015</v>
       </c>
       <c r="G61" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H61" t="n">
-        <v>1.63</v>
+        <v>18.5425</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2.666445086035864e-67</v>
+        <v>2.729694668348151e-67</v>
       </c>
       <c r="K61" t="n">
-        <v>1.281421616962445e-66</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0.9998875</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -8747,19 +8683,19 @@
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H62" t="n">
-        <v>99.795</v>
+        <v>89.31</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6.486318758726508e-68</v>
+        <v>2.707835634028802e-67</v>
       </c>
       <c r="K62" t="n">
-        <v>4.647429739996799e-67</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -8804,22 +8740,22 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H63" t="n">
-        <v>7.255</v>
+        <v>89.31</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.707835634028802e-67</v>
       </c>
       <c r="K63" t="n">
-        <v>4.647429739996799e-67</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -8864,28 +8800,28 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.205</v>
+        <v>10.69</v>
       </c>
       <c r="H64" t="n">
-        <v>2.33</v>
+        <v>89.31</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.707835634028802e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>4.647429739996799e-67</v>
+        <v>7.861824915320062e-67</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.99229375</v>
+        <v>1</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -8924,28 +8860,28 @@
         <v>416</v>
       </c>
       <c r="F65" t="n">
-        <v>5.57</v>
+        <v>11.41</v>
       </c>
       <c r="G65" t="n">
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>-92.45999999999999</v>
+        <v>-88.59</v>
       </c>
       <c r="I65" t="n">
-        <v>2925</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2.609313895507326e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K65" t="n">
-        <v>9.949153956817221e-61</v>
+        <v>1.697669506633043e-70</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1769976192677515</v>
+        <v>0</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -8984,28 +8920,28 @@
         <v>416</v>
       </c>
       <c r="F66" t="n">
-        <v>3.65</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>-94.19</v>
+        <v>-91.21000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.625471183048989e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K66" t="n">
-        <v>9.949153956817221e-61</v>
+        <v>1.697669506633043e-70</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1774107803254438</v>
+        <v>0</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -9044,28 +8980,28 @@
         <v>416</v>
       </c>
       <c r="F67" t="n">
-        <v>3.21</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G67" t="n">
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>-94.19</v>
+        <v>-91.21000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2.616561147174345e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K67" t="n">
-        <v>9.949153956817221e-61</v>
+        <v>1.697669506633043e-70</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1790403106508876</v>
+        <v>0</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -9104,28 +9040,28 @@
         <v>416</v>
       </c>
       <c r="F68" t="n">
-        <v>5.57</v>
+        <v>11.41</v>
       </c>
       <c r="G68" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H68" t="n">
-        <v>3.48</v>
+        <v>5.4725</v>
       </c>
       <c r="I68" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1.527014197472544e-69</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K68" t="n">
-        <v>1.37431277772529e-68</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9134615384615384</v>
+        <v>0.987449149408284</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -9164,28 +9100,28 @@
         <v>416</v>
       </c>
       <c r="F69" t="n">
-        <v>3.65</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H69" t="n">
-        <v>1.6075</v>
+        <v>2.852499999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>4430.5</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1.037936694942168e-56</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K69" t="n">
-        <v>3.39688372890164e-56</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.776702339127219</v>
+        <v>0.7854047244822485</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -9224,28 +9160,28 @@
         <v>416</v>
       </c>
       <c r="F70" t="n">
-        <v>3.21</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H70" t="n">
-        <v>1.185</v>
+        <v>2.852499999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>5221</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1.669870199611228e-54</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K70" t="n">
-        <v>5.227419755304713e-54</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7245198086168639</v>
+        <v>0.7460879715236687</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -9287,25 +9223,25 @@
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H71" t="n">
-        <v>96.91500000000001</v>
+        <v>94.955</v>
       </c>
       <c r="I71" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2.10118130457541e-61</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K71" t="n">
-        <v>9.455315870589344e-61</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8505512666420119</v>
+        <v>1</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -9347,25 +9283,25 @@
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H72" t="n">
-        <v>96.91500000000001</v>
+        <v>94.955</v>
       </c>
       <c r="I72" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>4.91990072267415e-61</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K72" t="n">
-        <v>1.686823104916851e-60</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8267063840606509</v>
+        <v>1</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -9407,25 +9343,25 @@
         <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>2.7675</v>
+        <v>5.045</v>
       </c>
       <c r="H73" t="n">
-        <v>96.91500000000001</v>
+        <v>94.955</v>
       </c>
       <c r="I73" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>4.919580436851137e-61</v>
+        <v>3.980014077887009e-71</v>
       </c>
       <c r="K73" t="n">
-        <v>1.686823104916851e-60</v>
+        <v>1.791006335049154e-70</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8216386603180473</v>
+        <v>1</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
